--- a/public/template-import-santri.xlsx
+++ b/public/template-import-santri.xlsx
@@ -1,42 +1,235 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Aldi Nitip\Hady Nitip\Project\buku-induk\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1C112-C551-47B5-B37A-821784601D80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="panduan" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>SERVER</author>
+  </authors>
+  <commentList>
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{D229EC09-8403-48DD-BC88-E86B30C2CCBF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>SMP Al-Lathifah:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+aktif, khusus, mutasi_keluar, lulus, wafat, drop_out</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+  <si>
+    <t>Nama lengkap *</t>
+  </si>
+  <si>
+    <t>NISN</t>
+  </si>
+  <si>
+    <t>NIK</t>
+  </si>
+  <si>
+    <t>NIS</t>
+  </si>
+  <si>
+    <t>NIPD</t>
+  </si>
+  <si>
+    <t>Nama panggilan</t>
+  </si>
+  <si>
+    <t>Tempat lahir</t>
+  </si>
+  <si>
+    <t>Tanggal lahir</t>
+  </si>
+  <si>
+    <t>Jenis kelamin (L/P)</t>
+  </si>
+  <si>
+    <t>Agama</t>
+  </si>
+  <si>
+    <t>Kewarganegaraan</t>
+  </si>
+  <si>
+    <t>Tempat tinggal</t>
+  </si>
+  <si>
+    <t>Transportasi</t>
+  </si>
+  <si>
+    <t>Anak ke</t>
+  </si>
+  <si>
+    <t>No. HP</t>
+  </si>
+  <si>
+    <t>Alamat</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>RW</t>
+  </si>
+  <si>
+    <t>Desa/kelurahan</t>
+  </si>
+  <si>
+    <t>Kecamatan</t>
+  </si>
+  <si>
+    <t>Kabupaten</t>
+  </si>
+  <si>
+    <t>No. akta</t>
+  </si>
+  <si>
+    <t>No. KK</t>
+  </si>
+  <si>
+    <t>Bantuan (KIP/PIP/KPS/PKH)</t>
+  </si>
+  <si>
+    <t>Status keluarga</t>
+  </si>
+  <si>
+    <t>Status santri</t>
+  </si>
+  <si>
+    <t>Tanggal masuk</t>
+  </si>
+  <si>
+    <t>Asal sekolah</t>
+  </si>
+  <si>
+    <t>Jalur masuk</t>
+  </si>
+  <si>
+    <t>Kamar (nomor)</t>
+  </si>
+  <si>
+    <t>Kelas (mis. 7A)</t>
+  </si>
+  <si>
+    <t>Nama ayah</t>
+  </si>
+  <si>
+    <t>Nama ibu</t>
+  </si>
+  <si>
+    <t>Nama wali</t>
+  </si>
+  <si>
+    <t>Pekerjaan ayah</t>
+  </si>
+  <si>
+    <t>Pekerjaan ibu</t>
+  </si>
+  <si>
+    <t>Penghasilan</t>
+  </si>
+  <si>
+    <t>Alamat wali</t>
+  </si>
+  <si>
+    <t>No. HP wali</t>
+  </si>
+  <si>
+    <t>Panduan import data santri</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1. Isi sheet "data". Baris pertama adalah header — jangan diubah. Data mulai baris 2.</t>
+  </si>
+  <si>
+    <t>2. Kolom "Nama lengkap" wajib diisi; kolom lain opsional.</t>
+  </si>
+  <si>
+    <t>3. Jenis kelamin: L atau P</t>
+  </si>
+  <si>
+    <t>4. Status santri: aktif, khusus, mutasi_keluar, lulus, wafat, drop_out</t>
+  </si>
+  <si>
+    <t>5. Status keluarga: yatim, yatim_piatu, dhuafa, umum</t>
+  </si>
+  <si>
+    <t>6. Kamar: nomor kamar (contoh: 3). Kelas: tingkat+rombel (contoh: 7A).</t>
+  </si>
+  <si>
+    <t>7. Isi nama ayah/ibu/wali agar wali santri ikut tercatat.</t>
+  </si>
+  <si>
+    <t>Contoh baris 2:</t>
+  </si>
+  <si>
+    <t>Ahmad Fauzi</t>
+  </si>
+  <si>
+    <t>0012345678</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>aktif</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>7A</t>
+  </si>
+  <si>
+    <t>Haji Salim</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -44,16 +237,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,18 +273,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,220 +638,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama lengkap *</v>
-      </c>
-      <c r="B1" t="str">
-        <v>NISN</v>
-      </c>
-      <c r="C1" t="str">
-        <v>NIK</v>
-      </c>
-      <c r="D1" t="str">
-        <v>NIS</v>
-      </c>
-      <c r="E1" t="str">
-        <v>NIPD</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Nama panggilan</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Tempat lahir</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Tanggal lahir</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Jenis kelamin (L/P)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Agama</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Kewarganegaraan</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Tempat tinggal</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Transportasi</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Anak ke</v>
-      </c>
-      <c r="O1" t="str">
-        <v>No. HP</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Alamat</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>RT</v>
-      </c>
-      <c r="R1" t="str">
-        <v>RW</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Desa/kelurahan</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Kecamatan</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Kabupaten</v>
-      </c>
-      <c r="V1" t="str">
-        <v>No. akta</v>
-      </c>
-      <c r="W1" t="str">
-        <v>No. KK</v>
-      </c>
-      <c r="X1" t="str">
-        <v>Bantuan (KIP/PIP/KPS/PKH)</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>Status keluarga</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Status santri</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Tanggal masuk</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Asal sekolah</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>Jalur masuk</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>Kamar (nomor)</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>Kelas (mis. 7A)</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>Nama ayah</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>Nama ibu</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>Nama wali</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>Pekerjaan ayah</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>Pekerjaan ibu</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>Penghasilan</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>Alamat wali</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>No. HP wali</v>
+    <row r="1" spans="1:39" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AM1"/>
+    <ignoredError sqref="A1:AM1" numberStoredAsText="1"/>
   </ignoredErrors>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Panduan import data santri</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1. Isi sheet "data". Baris pertama adalah header — jangan diubah. Data mulai baris 2.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2. Kolom "Nama lengkap" wajib diisi; kolom lain opsional.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3. Jenis kelamin: L atau P</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>4. Status santri: aktif, khusus, mutasi_keluar, lulus, wafat, drop_out</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5. Status keluarga: yatim, yatim_piatu, dhuafa, umum</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>6. Kamar: nomor kamar (contoh: 3). Kelas: tingkat+rombel (contoh: 7A).</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>7. Isi nama ayah/ibu/wali agar wali santri ikut tercatat.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Contoh baris 2:</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Ahmad Fauzi</v>
-      </c>
-      <c r="B12" t="str">
-        <v>0012345678</v>
-      </c>
-      <c r="C12" t="str">
-        <v>L</v>
-      </c>
-      <c r="D12" t="str">
-        <v>aktif</v>
-      </c>
-      <c r="E12" t="str">
-        <v>3</v>
-      </c>
-      <c r="F12" t="str">
-        <v>7A</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Haji Salim</v>
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
+    <ignoredError sqref="A1:G5 A7:G12 B6:G6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>